--- a/dataset/Non-Faulty/st_cross_thread_access.xlsx
+++ b/dataset/Non-Faulty/st_cross_thread_access.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +473,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pthread_mutex_t st_cross_thread_access_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_001_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_001_glb_data = 0; int *st_cross_thread_access_001_glb_ptr; pthread_mutex_t st_cross_thread_access_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_002_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; unsigned long st_cross_thread_access_002_glb_data = 0; int const st_cross_thread_access_002_var = 10; int arr1[5]={1,2,3,4,5}; int * st_cross_thread_access_002_glb_ptr = arr1; pthread_mutex_t st_cross_thread_access_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_003_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; float st_cross_thread_access_003_glb_data = 1000.0; float st_cross_thread_access_003_glb_data1 = 10.0; float *st_cross_thread_access_003_glb_ptr = &amp;st_cross_thread_access_003_glb_data1; pthread_mutex_t st_cross_thread_access_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char *buf1="String1"; char *buf2="String2"; char **pbuf[2] = {&amp;buf1, &amp;buf2}; pthread_mutex_t st_cross_thread_access_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_005_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_005_glb_data = 0; int st_cross_thread_access_005_thread_set = NO_THREAD; pthread_mutex_t st_cross_thread_access_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; st_cross_thread_access_006_s_001 s1 ={10,20}; st_cross_thread_access_006_s_001 *sptr = &amp;s1; extern volatile int vflag; void st_cross_thread_access_002 () { #if !defined(CHECKER_POLYSPACE) pthread_t tid1,tid2; intptr_t st_cross_thread_access_002_t1 = 10; intptr_t st_cross_thread_access_002_t2 = 10; pthread_mutex_init(&amp;st_cross_thread_access_002_glb_mutex, NULL); pthread_create(&amp;tid1, NULL, st_cross_thread_access_002_tsk_001, (void *)st_cross_thread_access_002_t1); sleep(1); pthread_mutex_init(&amp;st_cross_thread_access_002_glb_mutex_1, NULL); pthread_create(&amp;tid2, NULL, st_cross_thread_access_002_tsk_002, (void *)st_cross_thread_access_002_t2); pthread_join(tid1, NULL); pthread_join(tid2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void * st_cross_thread_access_002_tsk_002 (void * pram) { #if !defined(CHECKER_POLYSPACE) if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex_1); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex_1); } if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex_1); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; #if defined PRINT_DEBUG unsigned long ip = (unsigned long)pthread_self(); printf("Task2! Cross thread stack access, threadID # %lu! gbl2 = %lu \n",ip ,st_cross_thread_access_002_glb_data); #endif /* defined(PRINT_DEBUG) */ pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex_1); } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * st_cross_thread_access_002_tsk_001 (void * pram) { #if !defined(CHECKER_POLYSPACE) int arr[5] = {10,20,30,40,50}; if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; st_cross_thread_access_002_glb_ptr = arr; *st_cross_thread_access_002_glb_ptr = 200.0; pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex); } if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; #if defined PRINT_DEBUG unsigned long ip = (unsigned long)pthread_self(); printf("Task2! Cross thread stack access, threadID # %lu! gbl2 = %lu \n",ip ,st_cross_thread_access_002_glb_data); #endif /* defined(PRINT_DEBUG) */ pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex); } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t st_cross_thread_access_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_001_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_001_glb_data = 0; int *st_cross_thread_access_001_glb_ptr; pthread_mutex_t st_cross_thread_access_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_002_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; unsigned long st_cross_thread_access_002_glb_data = 0; int const st_cross_thread_access_002_var = 10; int arr1[5]={1,2,3,4,5}; int * st_cross_thread_access_002_glb_ptr = arr1; pthread_mutex_t st_cross_thread_access_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_003_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; float st_cross_thread_access_003_glb_data = 1000.0; float st_cross_thread_access_003_glb_data1 = 10.0; float *st_cross_thread_access_003_glb_ptr = &amp;st_cross_thread_access_003_glb_data1; pthread_mutex_t st_cross_thread_access_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char *buf1="String1"; char *buf2="String2"; char **pbuf[2] = {&amp;buf1, &amp;buf2}; pthread_mutex_t st_cross_thread_access_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_005_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_005_glb_data = 0; int st_cross_thread_access_005_thread_set = NO_THREAD; pthread_mutex_t st_cross_thread_access_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; st_cross_thread_access_006_s_001 s1 ={10,20}; st_cross_thread_access_006_s_001 *sptr = &amp;s1; extern volatile int vflag; void st_cross_thread_access_002 () { #if !defined(CHECKER_POLYSPACE) pthread_t tid1,tid2; intptr_t st_cross_thread_access_002_t1 = 10; intptr_t st_cross_thread_access_002_t2 = 10; pthread_mutex_init(&amp;st_cross_thread_access_002_glb_mutex, NULL); pthread_create(&amp;tid1, NULL, st_cross_thread_access_002_tsk_001, (void *)st_cross_thread_access_002_t1); sleep(1); pthread_mutex_init(&amp;st_cross_thread_access_002_glb_mutex_1, NULL); pthread_create(&amp;tid2, NULL, st_cross_thread_access_002_tsk_002, (void *)st_cross_thread_access_002_t2); pthread_join(tid1, NULL); pthread_join(tid2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void * st_cross_thread_access_002_tsk_001 (void * pram) { #if !defined(CHECKER_POLYSPACE) int arr[5] = {10,20,30,40,50}; if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; st_cross_thread_access_002_glb_ptr = arr; *st_cross_thread_access_002_glb_ptr = 200.0; pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex); } if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; #if defined PRINT_DEBUG unsigned long ip = (unsigned long)pthread_self(); printf("Task2! Cross thread stack access, threadID # %lu! gbl2 = %lu \n",ip ,st_cross_thread_access_002_glb_data); #endif /* defined(PRINT_DEBUG) */ pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex); } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * st_cross_thread_access_002_tsk_002 (void * pram) { #if !defined(CHECKER_POLYSPACE) if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex_1); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex_1); } if(st_cross_thread_access_002_var == (intptr_t)pram) { pthread_mutex_lock(&amp;st_cross_thread_access_002_glb_mutex_1); st_cross_thread_access_002_glb_data = (st_cross_thread_access_002_glb_data % 100) + 1; #if defined PRINT_DEBUG unsigned long ip = (unsigned long)pthread_self(); printf("Task2! Cross thread stack access, threadID # %lu! gbl2 = %lu \n",ip ,st_cross_thread_access_002_glb_data); #endif /* defined(PRINT_DEBUG) */ pthread_mutex_unlock(&amp;st_cross_thread_access_002_glb_mutex_1); } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/st_cross_thread_access.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
